--- a/informes_data/Euroleague/2025-26/Regular_Season/aggregate_individual/AGG_IND_FC BAYERN MUNICH.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/aggregate_individual/AGG_IND_FC BAYERN MUNICH.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>O. DA SILVA</t>
+          <t>J. JESSUP</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D2" t="n">
-        <v>52.2559</v>
+        <v>38.4668</v>
       </c>
       <c r="E2" t="n">
-        <v>34.8127</v>
+        <v>15.3798</v>
       </c>
       <c r="F2" t="n">
-        <v>17.4433</v>
+        <v>23.0864</v>
       </c>
       <c r="G2" t="n">
-        <v>4.8838</v>
+        <v>10.6036</v>
       </c>
       <c r="H2" t="n">
-        <v>9.4053</v>
+        <v>13.8436</v>
       </c>
       <c r="I2" t="n">
-        <v>-4.5215</v>
+        <v>-3.239899999999998</v>
       </c>
       <c r="J2" t="n">
-        <v>25.0531</v>
+        <v>33.2688</v>
       </c>
       <c r="K2" t="n">
-        <v>22.4677</v>
+        <v>24.8421</v>
       </c>
       <c r="L2" t="n">
-        <v>2.585500000000001</v>
+        <v>8.4269</v>
       </c>
       <c r="M2" t="n">
-        <v>-20.1693</v>
+        <v>-22.6654</v>
       </c>
       <c r="N2" t="n">
-        <v>-13.0624</v>
+        <v>-10.9988</v>
       </c>
       <c r="O2" t="n">
-        <v>-7.1071</v>
+        <v>-11.6666</v>
       </c>
       <c r="P2" t="n">
-        <v>12.062</v>
+        <v>30.8503</v>
       </c>
       <c r="Q2" t="n">
-        <v>-32.9376</v>
+        <v>-30.1543</v>
       </c>
       <c r="R2" t="n">
-        <v>44.9992</v>
+        <v>61.0038</v>
       </c>
       <c r="S2" t="n">
-        <v>28.9395</v>
+        <v>-3.7126</v>
       </c>
       <c r="T2" t="n">
-        <v>26.1881</v>
+        <v>-3.4243</v>
       </c>
       <c r="U2" t="n">
-        <v>2.7516</v>
+        <v>-0.2884000000000002</v>
       </c>
       <c r="V2" t="n">
-        <v>6.371100000000001</v>
+        <v>0.7263999999999999</v>
       </c>
       <c r="W2" t="n">
-        <v>16.5084</v>
+        <v>15.6887</v>
       </c>
       <c r="X2" t="n">
-        <v>-10.1373</v>
+        <v>-14.9623</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. JESSUP</t>
+          <t>O. DA SILVA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D3" t="n">
-        <v>29.3787</v>
+        <v>35.3461</v>
       </c>
       <c r="E3" t="n">
-        <v>10.4106</v>
+        <v>17.619</v>
       </c>
       <c r="F3" t="n">
-        <v>18.9679</v>
+        <v>17.7266</v>
       </c>
       <c r="G3" t="n">
-        <v>10.6036</v>
+        <v>4.8838</v>
       </c>
       <c r="H3" t="n">
-        <v>13.8436</v>
+        <v>9.4053</v>
       </c>
       <c r="I3" t="n">
-        <v>-3.239899999999998</v>
+        <v>-4.5215</v>
       </c>
       <c r="J3" t="n">
-        <v>33.2688</v>
+        <v>25.0531</v>
       </c>
       <c r="K3" t="n">
-        <v>24.8421</v>
+        <v>22.4677</v>
       </c>
       <c r="L3" t="n">
-        <v>8.4269</v>
+        <v>2.585500000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>-22.6654</v>
+        <v>-20.1693</v>
       </c>
       <c r="N3" t="n">
-        <v>-10.9988</v>
+        <v>-13.0624</v>
       </c>
       <c r="O3" t="n">
-        <v>-11.6666</v>
+        <v>-7.1071</v>
       </c>
       <c r="P3" t="n">
-        <v>30.8503</v>
+        <v>12.062</v>
       </c>
       <c r="Q3" t="n">
-        <v>-30.1543</v>
+        <v>-32.9376</v>
       </c>
       <c r="R3" t="n">
-        <v>61.0038</v>
+        <v>44.9992</v>
       </c>
       <c r="S3" t="n">
-        <v>-12.8006</v>
+        <v>12.0295</v>
       </c>
       <c r="T3" t="n">
-        <v>-8.3932</v>
+        <v>8.994400000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>-4.4073</v>
+        <v>3.0347</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7263999999999999</v>
+        <v>6.371100000000001</v>
       </c>
       <c r="W3" t="n">
-        <v>15.6887</v>
+        <v>16.5084</v>
       </c>
       <c r="X3" t="n">
-        <v>-14.9623</v>
+        <v>-10.1373</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V. LUCIC</t>
+          <t>N. DIMITRIJEVIC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="D4" t="n">
-        <v>7.9361</v>
+        <v>15.6203</v>
       </c>
       <c r="E4" t="n">
-        <v>3.3988</v>
+        <v>5.0929</v>
       </c>
       <c r="F4" t="n">
-        <v>4.536999999999999</v>
+        <v>10.5275</v>
       </c>
       <c r="G4" t="n">
-        <v>-20.5573</v>
+        <v>29.9767</v>
       </c>
       <c r="H4" t="n">
-        <v>-11.5006</v>
+        <v>6.8122</v>
       </c>
       <c r="I4" t="n">
-        <v>-9.0563</v>
+        <v>23.1644</v>
       </c>
       <c r="J4" t="n">
-        <v>16.6499</v>
+        <v>37.9488</v>
       </c>
       <c r="K4" t="n">
-        <v>12.8818</v>
+        <v>14.0737</v>
       </c>
       <c r="L4" t="n">
-        <v>3.7683</v>
+        <v>23.8753</v>
       </c>
       <c r="M4" t="n">
-        <v>-37.207</v>
+        <v>-7.9724</v>
       </c>
       <c r="N4" t="n">
-        <v>-24.3825</v>
+        <v>-7.2617</v>
       </c>
       <c r="O4" t="n">
-        <v>-12.8246</v>
+        <v>-0.7104999999999997</v>
       </c>
       <c r="P4" t="n">
-        <v>20.8758</v>
+        <v>-24.1231</v>
       </c>
       <c r="Q4" t="n">
-        <v>-35.0254</v>
+        <v>-48.4778</v>
       </c>
       <c r="R4" t="n">
-        <v>55.9008</v>
+        <v>24.3551</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.606999999999999</v>
+        <v>-2.4841</v>
       </c>
       <c r="T4" t="n">
-        <v>-9.665699999999999</v>
+        <v>-3.346</v>
       </c>
       <c r="U4" t="n">
-        <v>8.0588</v>
+        <v>0.8617999999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>9.224399999999999</v>
+        <v>12.2507</v>
       </c>
       <c r="W4" t="n">
-        <v>31.4396</v>
+        <v>18.9675</v>
       </c>
       <c r="X4" t="n">
-        <v>-22.2152</v>
+        <v>-6.7168</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N. DIMITRIJEVIC</t>
+          <t>V. LUCIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,70 +796,70 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="D5" t="n">
-        <v>7.922499999999999</v>
+        <v>14.2745</v>
       </c>
       <c r="E5" t="n">
-        <v>0.09989999999999899</v>
+        <v>8.269900000000002</v>
       </c>
       <c r="F5" t="n">
-        <v>7.822900000000001</v>
+        <v>6.004600000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>29.9767</v>
+        <v>-20.5573</v>
       </c>
       <c r="H5" t="n">
-        <v>6.8122</v>
+        <v>-11.5006</v>
       </c>
       <c r="I5" t="n">
-        <v>23.1644</v>
+        <v>-9.0563</v>
       </c>
       <c r="J5" t="n">
-        <v>37.9488</v>
+        <v>16.6499</v>
       </c>
       <c r="K5" t="n">
-        <v>14.0737</v>
+        <v>12.8818</v>
       </c>
       <c r="L5" t="n">
-        <v>23.8753</v>
+        <v>3.7683</v>
       </c>
       <c r="M5" t="n">
-        <v>-7.9724</v>
+        <v>-37.207</v>
       </c>
       <c r="N5" t="n">
-        <v>-7.2617</v>
+        <v>-24.3825</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7104999999999997</v>
+        <v>-12.8246</v>
       </c>
       <c r="P5" t="n">
-        <v>-24.1231</v>
+        <v>20.8758</v>
       </c>
       <c r="Q5" t="n">
-        <v>-48.4778</v>
+        <v>-35.0254</v>
       </c>
       <c r="R5" t="n">
-        <v>24.3551</v>
+        <v>55.9008</v>
       </c>
       <c r="S5" t="n">
-        <v>-10.1816</v>
+        <v>4.7317</v>
       </c>
       <c r="T5" t="n">
-        <v>-8.338800000000001</v>
+        <v>-4.7949</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.8427</v>
+        <v>9.5266</v>
       </c>
       <c r="V5" t="n">
-        <v>12.2507</v>
+        <v>9.224399999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>18.9675</v>
+        <v>31.4396</v>
       </c>
       <c r="X5" t="n">
-        <v>-6.7168</v>
+        <v>-22.2152</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>26</v>
       </c>
       <c r="D6" t="n">
-        <v>6.100300000000001</v>
+        <v>9.851900000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>3.7416</v>
+        <v>4.991700000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>2.3587</v>
+        <v>4.8604</v>
       </c>
       <c r="G6" t="n">
         <v>11.8341</v>
@@ -922,13 +922,13 @@
         <v>33.8654</v>
       </c>
       <c r="S6" t="n">
-        <v>-3.0661</v>
+        <v>0.6858999999999997</v>
       </c>
       <c r="T6" t="n">
-        <v>-2.9074</v>
+        <v>-1.6574</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1585999999999998</v>
+        <v>2.3431</v>
       </c>
       <c r="V6" t="n">
         <v>-5.2192</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. VOIGTMANN</t>
+          <t>A. OBST</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="D7" t="n">
-        <v>3.4572</v>
+        <v>4.880199999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>-4.4558</v>
+        <v>-4.4697</v>
       </c>
       <c r="F7" t="n">
-        <v>7.913200000000002</v>
+        <v>9.350099999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>1.4425</v>
+        <v>-12.7081</v>
       </c>
       <c r="H7" t="n">
-        <v>0.02369999999999967</v>
+        <v>-18.2003</v>
       </c>
       <c r="I7" t="n">
-        <v>1.4187</v>
+        <v>5.492400000000002</v>
       </c>
       <c r="J7" t="n">
-        <v>15.4504</v>
+        <v>30.9293</v>
       </c>
       <c r="K7" t="n">
-        <v>6.4514</v>
+        <v>7.5809</v>
       </c>
       <c r="L7" t="n">
-        <v>8.999000000000001</v>
+        <v>23.3481</v>
       </c>
       <c r="M7" t="n">
-        <v>-14.008</v>
+        <v>-43.6372</v>
       </c>
       <c r="N7" t="n">
-        <v>-6.428</v>
+        <v>-25.7817</v>
       </c>
       <c r="O7" t="n">
-        <v>-7.580299999999999</v>
+        <v>-17.8559</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.6959000000000006</v>
+        <v>2.783599999999999</v>
       </c>
       <c r="Q7" t="n">
-        <v>-23.8913</v>
+        <v>-65.41079999999999</v>
       </c>
       <c r="R7" t="n">
-        <v>23.1955</v>
+        <v>68.19409999999999</v>
       </c>
       <c r="S7" t="n">
-        <v>10.3891</v>
+        <v>-6.023499999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>1.5568</v>
+        <v>-7.1839</v>
       </c>
       <c r="U7" t="n">
-        <v>8.832100000000001</v>
+        <v>1.1605</v>
       </c>
       <c r="V7" t="n">
-        <v>-7.6783</v>
+        <v>20.8283</v>
       </c>
       <c r="W7" t="n">
-        <v>2.428</v>
+        <v>37.1949</v>
       </c>
       <c r="X7" t="n">
-        <v>-10.1063</v>
+        <v>-16.3666</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. KRATZER</t>
+          <t>J. VOIGTMANN</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="D8" t="n">
-        <v>-5.3551</v>
+        <v>-1.4898</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.356</v>
+        <v>-6.484399999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9993</v>
+        <v>4.994400000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3618000000000003</v>
+        <v>1.4425</v>
       </c>
       <c r="H8" t="n">
-        <v>1.1914</v>
+        <v>0.02369999999999967</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8295</v>
+        <v>1.4187</v>
       </c>
       <c r="J8" t="n">
-        <v>2.6921</v>
+        <v>15.4504</v>
       </c>
       <c r="K8" t="n">
-        <v>1.1462</v>
+        <v>6.4514</v>
       </c>
       <c r="L8" t="n">
-        <v>1.5458</v>
+        <v>8.999000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.3303</v>
+        <v>-14.008</v>
       </c>
       <c r="N8" t="n">
-        <v>0.04509999999999975</v>
+        <v>-6.428</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.3753</v>
+        <v>-7.580299999999999</v>
       </c>
       <c r="P8" t="n">
-        <v>-3.0155</v>
+        <v>-0.6959000000000006</v>
       </c>
       <c r="Q8" t="n">
-        <v>-6.0308</v>
+        <v>-23.8913</v>
       </c>
       <c r="R8" t="n">
-        <v>3.0155</v>
+        <v>23.1955</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4040999999999999</v>
+        <v>5.4416</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0175</v>
+        <v>-0.4721999999999998</v>
       </c>
       <c r="U8" t="n">
-        <v>1.4216</v>
+        <v>5.9136</v>
       </c>
       <c r="V8" t="n">
-        <v>-3.1059</v>
+        <v>-7.6783</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.428</v>
       </c>
       <c r="X8" t="n">
-        <v>-3.1059</v>
+        <v>-10.1063</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N. GIFFEY</t>
+          <t>S. JOVIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="D9" t="n">
-        <v>-8.236000000000001</v>
+        <v>-2.6973</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003300000000000747</v>
+        <v>-1.7718</v>
       </c>
       <c r="F9" t="n">
-        <v>-8.239000000000001</v>
+        <v>-0.9253</v>
       </c>
       <c r="G9" t="n">
-        <v>-16.2751</v>
+        <v>13.4876</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4676000000000001</v>
+        <v>2.7</v>
       </c>
       <c r="I9" t="n">
-        <v>-16.7434</v>
+        <v>10.7877</v>
       </c>
       <c r="J9" t="n">
-        <v>8.4574</v>
+        <v>33.1097</v>
       </c>
       <c r="K9" t="n">
-        <v>6.1437</v>
+        <v>14.949</v>
       </c>
       <c r="L9" t="n">
-        <v>2.313400000000001</v>
+        <v>18.1605</v>
       </c>
       <c r="M9" t="n">
-        <v>-24.7327</v>
+        <v>-19.6224</v>
       </c>
       <c r="N9" t="n">
-        <v>-5.6764</v>
+        <v>-12.2494</v>
       </c>
       <c r="O9" t="n">
-        <v>-19.0567</v>
+        <v>-7.3729</v>
       </c>
       <c r="P9" t="n">
-        <v>12.9894</v>
+        <v>-9.5099</v>
       </c>
       <c r="Q9" t="n">
-        <v>-19.9484</v>
+        <v>-37.5765</v>
       </c>
       <c r="R9" t="n">
-        <v>32.9377</v>
+        <v>28.0664</v>
       </c>
       <c r="S9" t="n">
-        <v>-5.7868</v>
+        <v>1.1451</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7404999999999999</v>
+        <v>-0.9474999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>-6.5276</v>
+        <v>2.093</v>
       </c>
       <c r="V9" t="n">
-        <v>0.8371999999999998</v>
+        <v>-7.82</v>
       </c>
       <c r="W9" t="n">
-        <v>10.7531</v>
+        <v>3.642</v>
       </c>
       <c r="X9" t="n">
-        <v>-9.915900000000001</v>
+        <v>-11.462</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. MCCORMACK</t>
+          <t>N. GIFFEY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,70 +1186,70 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D10" t="n">
-        <v>-8.538</v>
+        <v>-2.9546</v>
       </c>
       <c r="E10" t="n">
-        <v>-6.081200000000001</v>
+        <v>1.147099999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.4567</v>
+        <v>-4.1012</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.07469999999999943</v>
+        <v>-16.2751</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.5292</v>
+        <v>0.4676000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>1.4544</v>
+        <v>-16.7434</v>
       </c>
       <c r="J10" t="n">
-        <v>16.58</v>
+        <v>8.4574</v>
       </c>
       <c r="K10" t="n">
-        <v>11.5042</v>
+        <v>6.1437</v>
       </c>
       <c r="L10" t="n">
-        <v>5.0755</v>
+        <v>2.313400000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>-16.6548</v>
+        <v>-24.7327</v>
       </c>
       <c r="N10" t="n">
-        <v>-13.0335</v>
+        <v>-5.6764</v>
       </c>
       <c r="O10" t="n">
-        <v>-3.6211</v>
+        <v>-19.0567</v>
       </c>
       <c r="P10" t="n">
-        <v>-6.2626</v>
+        <v>12.9894</v>
       </c>
       <c r="Q10" t="n">
-        <v>-41.5196</v>
+        <v>-19.9484</v>
       </c>
       <c r="R10" t="n">
-        <v>35.2571</v>
+        <v>32.9377</v>
       </c>
       <c r="S10" t="n">
-        <v>9.137200000000002</v>
+        <v>-0.5053</v>
       </c>
       <c r="T10" t="n">
-        <v>6.1507</v>
+        <v>1.8841</v>
       </c>
       <c r="U10" t="n">
-        <v>2.9868</v>
+        <v>-2.3898</v>
       </c>
       <c r="V10" t="n">
-        <v>-11.3377</v>
+        <v>0.8371999999999998</v>
       </c>
       <c r="W10" t="n">
-        <v>12.7071</v>
+        <v>10.7531</v>
       </c>
       <c r="X10" t="n">
-        <v>-24.0449</v>
+        <v>-9.915900000000001</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.738</v>
+        <v>-5.1782</v>
       </c>
       <c r="E11" t="n">
-        <v>-10.1889</v>
+        <v>-7.3817</v>
       </c>
       <c r="F11" t="n">
-        <v>1.450999999999999</v>
+        <v>2.2037</v>
       </c>
       <c r="G11" t="n">
         <v>-6.6402</v>
@@ -1312,13 +1312,13 @@
         <v>12.9893</v>
       </c>
       <c r="S11" t="n">
-        <v>-4.7759</v>
+        <v>-1.2157</v>
       </c>
       <c r="T11" t="n">
-        <v>-3.1947</v>
+        <v>-0.3875</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.581</v>
+        <v>-0.8280999999999999</v>
       </c>
       <c r="V11" t="n">
         <v>1.7501</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S. JOVIC</t>
+          <t>L. KRATZER</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,70 +1342,70 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>-10.5017</v>
+        <v>-5.2112</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.3667</v>
+        <v>-4.3248</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.1352</v>
+        <v>-0.8863999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>13.4876</v>
+        <v>0.3618000000000003</v>
       </c>
       <c r="H12" t="n">
-        <v>2.7</v>
+        <v>1.1914</v>
       </c>
       <c r="I12" t="n">
-        <v>10.7877</v>
+        <v>-0.8295</v>
       </c>
       <c r="J12" t="n">
-        <v>33.1097</v>
+        <v>2.6921</v>
       </c>
       <c r="K12" t="n">
-        <v>14.949</v>
+        <v>1.1462</v>
       </c>
       <c r="L12" t="n">
-        <v>18.1605</v>
+        <v>1.5458</v>
       </c>
       <c r="M12" t="n">
-        <v>-19.6224</v>
+        <v>-2.3303</v>
       </c>
       <c r="N12" t="n">
-        <v>-12.2494</v>
+        <v>0.04509999999999975</v>
       </c>
       <c r="O12" t="n">
-        <v>-7.3729</v>
+        <v>-2.3753</v>
       </c>
       <c r="P12" t="n">
-        <v>-9.5099</v>
+        <v>-3.0155</v>
       </c>
       <c r="Q12" t="n">
-        <v>-37.5765</v>
+        <v>-6.0308</v>
       </c>
       <c r="R12" t="n">
-        <v>28.0664</v>
+        <v>3.0155</v>
       </c>
       <c r="S12" t="n">
-        <v>-6.6593</v>
+        <v>0.5485</v>
       </c>
       <c r="T12" t="n">
-        <v>-6.5422</v>
+        <v>-0.9861</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1170999999999998</v>
+        <v>1.5345</v>
       </c>
       <c r="V12" t="n">
-        <v>-7.82</v>
+        <v>-3.1059</v>
       </c>
       <c r="W12" t="n">
-        <v>3.642</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-11.462</v>
+        <v>-3.1059</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>11</v>
       </c>
       <c r="D13" t="n">
-        <v>-13.3449</v>
+        <v>-5.5505</v>
       </c>
       <c r="E13" t="n">
-        <v>-13.5682</v>
+        <v>-8.9368</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2234000000000003</v>
+        <v>3.3862</v>
       </c>
       <c r="G13" t="n">
         <v>-0.03289999999999971</v>
@@ -1468,13 +1468,13 @@
         <v>20.1799</v>
       </c>
       <c r="S13" t="n">
-        <v>-9.4572</v>
+        <v>-1.6627</v>
       </c>
       <c r="T13" t="n">
-        <v>-7.4787</v>
+        <v>-2.8473</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.9786</v>
+        <v>1.1843</v>
       </c>
       <c r="V13" t="n">
         <v>9.366099999999999</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. OBST</t>
+          <t>D. MCCORMACK</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="D14" t="n">
-        <v>-25.5517</v>
+        <v>-15.5032</v>
       </c>
       <c r="E14" t="n">
-        <v>-23.7188</v>
+        <v>-12.6043</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.832699999999999</v>
+        <v>-2.8994</v>
       </c>
       <c r="G14" t="n">
-        <v>-12.7081</v>
+        <v>-0.07469999999999943</v>
       </c>
       <c r="H14" t="n">
-        <v>-18.2003</v>
+        <v>-1.5292</v>
       </c>
       <c r="I14" t="n">
-        <v>5.492400000000002</v>
+        <v>1.4544</v>
       </c>
       <c r="J14" t="n">
-        <v>30.9293</v>
+        <v>16.58</v>
       </c>
       <c r="K14" t="n">
-        <v>7.5809</v>
+        <v>11.5042</v>
       </c>
       <c r="L14" t="n">
-        <v>23.3481</v>
+        <v>5.0755</v>
       </c>
       <c r="M14" t="n">
-        <v>-43.6372</v>
+        <v>-16.6548</v>
       </c>
       <c r="N14" t="n">
-        <v>-25.7817</v>
+        <v>-13.0335</v>
       </c>
       <c r="O14" t="n">
-        <v>-17.8559</v>
+        <v>-3.6211</v>
       </c>
       <c r="P14" t="n">
-        <v>2.783599999999999</v>
+        <v>-6.2626</v>
       </c>
       <c r="Q14" t="n">
-        <v>-65.41079999999999</v>
+        <v>-41.5196</v>
       </c>
       <c r="R14" t="n">
-        <v>68.19409999999999</v>
+        <v>35.2571</v>
       </c>
       <c r="S14" t="n">
-        <v>-36.455</v>
+        <v>2.172</v>
       </c>
       <c r="T14" t="n">
-        <v>-26.4329</v>
+        <v>-0.3720999999999998</v>
       </c>
       <c r="U14" t="n">
-        <v>-10.0224</v>
+        <v>2.5442</v>
       </c>
       <c r="V14" t="n">
-        <v>20.8283</v>
+        <v>-11.3377</v>
       </c>
       <c r="W14" t="n">
-        <v>37.1949</v>
+        <v>12.7071</v>
       </c>
       <c r="X14" t="n">
-        <v>-16.3666</v>
+        <v>-24.0449</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>37</v>
       </c>
       <c r="D15" t="n">
-        <v>-27.5955</v>
+        <v>-25.2664</v>
       </c>
       <c r="E15" t="n">
-        <v>-18.4316</v>
+        <v>-16.7888</v>
       </c>
       <c r="F15" t="n">
-        <v>-9.163799999999998</v>
+        <v>-8.477500000000001</v>
       </c>
       <c r="G15" t="n">
         <v>-8.114699999999999</v>
@@ -1624,13 +1624,13 @@
         <v>61.0037</v>
       </c>
       <c r="S15" t="n">
-        <v>-3.5896</v>
+        <v>-1.26</v>
       </c>
       <c r="T15" t="n">
-        <v>-7.1722</v>
+        <v>-5.529</v>
       </c>
       <c r="U15" t="n">
-        <v>3.5827</v>
+        <v>4.2687</v>
       </c>
       <c r="V15" t="n">
         <v>-28.6484</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>W. GABRIEL</t>
+          <t>X. RATHAN-MAYES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>-43.31</v>
+        <v>-53.3554</v>
       </c>
       <c r="E16" t="n">
-        <v>-21.8024</v>
+        <v>-47.4016</v>
       </c>
       <c r="F16" t="n">
-        <v>-21.5075</v>
+        <v>-5.9535</v>
       </c>
       <c r="G16" t="n">
-        <v>-16.2627</v>
+        <v>-36.2435</v>
       </c>
       <c r="H16" t="n">
-        <v>-2.884599999999999</v>
+        <v>-13.0359</v>
       </c>
       <c r="I16" t="n">
-        <v>-13.3779</v>
+        <v>-23.2072</v>
       </c>
       <c r="J16" t="n">
-        <v>14.8953</v>
+        <v>-11.8142</v>
       </c>
       <c r="K16" t="n">
-        <v>7.6553</v>
+        <v>-0.4761999999999993</v>
       </c>
       <c r="L16" t="n">
-        <v>7.24</v>
+        <v>-11.338</v>
       </c>
       <c r="M16" t="n">
-        <v>-31.1573</v>
+        <v>-24.4289</v>
       </c>
       <c r="N16" t="n">
-        <v>-10.5393</v>
+        <v>-12.56</v>
       </c>
       <c r="O16" t="n">
-        <v>-20.6178</v>
+        <v>-11.869</v>
       </c>
       <c r="P16" t="n">
-        <v>-19.2521</v>
+        <v>-8.118200000000002</v>
       </c>
       <c r="Q16" t="n">
-        <v>-64.7149</v>
+        <v>-42.2158</v>
       </c>
       <c r="R16" t="n">
-        <v>45.4629</v>
+        <v>34.0974</v>
       </c>
       <c r="S16" t="n">
-        <v>26.4529</v>
+        <v>-4.4526</v>
       </c>
       <c r="T16" t="n">
-        <v>26.8687</v>
+        <v>-6.08</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4162000000000001</v>
+        <v>1.6272</v>
       </c>
       <c r="V16" t="n">
-        <v>-34.2483</v>
+        <v>-4.541400000000001</v>
       </c>
       <c r="W16" t="n">
-        <v>1.148</v>
+        <v>12.7071</v>
       </c>
       <c r="X16" t="n">
-        <v>-35.3963</v>
+        <v>-17.2485</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X. RATHAN-MAYES</t>
+          <t>W. GABRIEL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,70 +1732,70 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>-63.0047</v>
+        <v>-60.7295</v>
       </c>
       <c r="E17" t="n">
-        <v>-55.0647</v>
+        <v>-41.0875</v>
       </c>
       <c r="F17" t="n">
-        <v>-7.9402</v>
+        <v>-19.6418</v>
       </c>
       <c r="G17" t="n">
-        <v>-36.2435</v>
+        <v>-16.2627</v>
       </c>
       <c r="H17" t="n">
-        <v>-13.0359</v>
+        <v>-2.884599999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>-23.2072</v>
+        <v>-13.3779</v>
       </c>
       <c r="J17" t="n">
-        <v>-11.8142</v>
+        <v>14.8953</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.4761999999999993</v>
+        <v>7.6553</v>
       </c>
       <c r="L17" t="n">
-        <v>-11.338</v>
+        <v>7.24</v>
       </c>
       <c r="M17" t="n">
-        <v>-24.4289</v>
+        <v>-31.1573</v>
       </c>
       <c r="N17" t="n">
-        <v>-12.56</v>
+        <v>-10.5393</v>
       </c>
       <c r="O17" t="n">
-        <v>-11.869</v>
+        <v>-20.6178</v>
       </c>
       <c r="P17" t="n">
-        <v>-8.118200000000002</v>
+        <v>-19.2521</v>
       </c>
       <c r="Q17" t="n">
-        <v>-42.2158</v>
+        <v>-64.7149</v>
       </c>
       <c r="R17" t="n">
-        <v>34.0974</v>
+        <v>45.4629</v>
       </c>
       <c r="S17" t="n">
-        <v>-14.1019</v>
+        <v>9.0329</v>
       </c>
       <c r="T17" t="n">
-        <v>-13.7424</v>
+        <v>7.583799999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3597</v>
+        <v>1.4494</v>
       </c>
       <c r="V17" t="n">
-        <v>-4.541400000000001</v>
+        <v>-34.2483</v>
       </c>
       <c r="W17" t="n">
-        <v>12.7071</v>
+        <v>1.148</v>
       </c>
       <c r="X17" t="n">
-        <v>-17.2485</v>
+        <v>-35.3963</v>
       </c>
     </row>
     <row r="18">
@@ -1813,22 +1813,22 @@
         <v>37</v>
       </c>
       <c r="D18" t="n">
-        <v>-107.1249</v>
+        <v>-59.49629999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>-112.5674</v>
+        <v>-98.75099999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>5.442999999999998</v>
+        <v>39.2548</v>
       </c>
       <c r="G18" t="n">
-        <v>-44.31909999999999</v>
+        <v>-44.3191</v>
       </c>
       <c r="H18" t="n">
-        <v>-30.66649999999999</v>
+        <v>-30.6665</v>
       </c>
       <c r="I18" t="n">
-        <v>-13.65199999999999</v>
+        <v>-13.652</v>
       </c>
       <c r="J18" t="n">
         <v>292.6928</v>
@@ -1849,22 +1849,22 @@
         <v>-165.0488</v>
       </c>
       <c r="P18" t="n">
-        <v>11.59919999999999</v>
+        <v>11.59919999999998</v>
       </c>
       <c r="Q18" t="n">
         <v>-572.9261</v>
       </c>
       <c r="R18" t="n">
-        <v>584.5237999999999</v>
+        <v>584.5238000000001</v>
       </c>
       <c r="S18" t="n">
-        <v>-33.15819999999999</v>
+        <v>14.4707</v>
       </c>
       <c r="T18" t="n">
-        <v>-33.3809</v>
+        <v>-19.5659</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2223999999999995</v>
+        <v>34.0353</v>
       </c>
       <c r="V18" t="n">
         <v>-41.24490000000001</v>
